--- a/data/analysis_pixtral_12b_no_reid/visual_relation_eval_pixtral_12b_no_reid.xlsx
+++ b/data/analysis_pixtral_12b_no_reid/visual_relation_eval_pixtral_12b_no_reid.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="22">
   <si>
     <t>relation</t>
   </si>
@@ -70,22 +70,16 @@
     <t>support</t>
   </si>
   <si>
-    <t>carrying</t>
+    <t>physical_altercation</t>
+  </si>
+  <si>
+    <t>running</t>
   </si>
   <si>
     <t>enter_or_exit_vehicle</t>
   </si>
   <si>
-    <t>explosion_visible</t>
-  </si>
-  <si>
-    <t>gunshot_visible</t>
-  </si>
-  <si>
-    <t>physical_altercation</t>
-  </si>
-  <si>
-    <t>running</t>
+    <t>carrying</t>
   </si>
   <si>
     <t>suspicious_near_vehicle</t>
@@ -94,18 +88,44 @@
     <t>vehicle_collision</t>
   </si>
   <si>
+    <t>gunshot_visible</t>
+  </si>
+  <si>
+    <t>explosion_visible</t>
+  </si>
+  <si>
     <t>scene</t>
+  </si>
+  <si>
+    <t>in_gt</t>
+  </si>
+  <si>
+    <t>in_vlm</t>
   </si>
   <si>
     <t>result</t>
   </si>
+  <si>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -121,7 +141,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -129,12 +149,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -433,28 +471,28 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -463,22 +501,22 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>5</v>
@@ -489,25 +527,25 @@
         <v>9</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>0.545</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H3">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -515,25 +553,25 @@
         <v>10</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>0.188</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>0.286</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H4">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -541,25 +579,25 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>0.556</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>0.714</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -567,22 +605,22 @@
         <v>12</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>0.227</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>0.37</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H6">
         <v>5</v>
@@ -593,25 +631,25 @@
         <v>13</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>0.615</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G7">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -619,25 +657,25 @@
         <v>14</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H8">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -645,25 +683,25 @@
         <v>15</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -673,21 +711,27 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>12</v>
       </c>
@@ -695,18 +739,64 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>12</v>
       </c>
       <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="C3" t="s">
-        <v>6</v>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -716,21 +806,27 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>13</v>
       </c>
@@ -738,17 +834,29 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
         <v>6</v>
       </c>
     </row>
@@ -759,21 +867,27 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>14</v>
       </c>
@@ -781,18 +895,81 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>14</v>
       </c>
       <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="C3" t="s">
-        <v>6</v>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -802,253 +979,570 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>15</v>
       </c>
       <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
         <v>15</v>
       </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>16</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
       <c r="C2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>17</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
+        <v>18</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>19</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5">
+        <v>20</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1058,29 +1552,58 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1090,29 +1613,58 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1122,29 +1674,41 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1154,29 +1718,58 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>30</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1186,21 +1779,27 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>31</v>
       </c>
@@ -1208,18 +1807,64 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1229,21 +1874,27 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>32</v>
       </c>
@@ -1251,18 +1902,47 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1272,29 +1952,75 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>33</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>33</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1304,29 +2030,75 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>34</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
+        <v>34</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1336,29 +2108,92 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>35</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
+        <v>35</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5">
+        <v>35</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1368,29 +2203,75 @@
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>36</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>36</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
+        <v>36</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1400,29 +2281,75 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>5</v>
       </c>
       <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
         <v>12</v>
       </c>
-      <c r="C2" t="s">
-        <v>6</v>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1432,29 +2359,41 @@
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>37</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1464,29 +2403,41 @@
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>38</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1496,29 +2447,41 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1528,51 +2491,126 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>7</v>
       </c>
       <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="C4" t="s">
-        <v>6</v>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1582,39 +2620,91 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1625,40 +2715,109 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1668,40 +2827,58 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1711,40 +2888,109 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>11</v>
       </c>
       <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="C3" t="s">
-        <v>6</v>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
